--- a/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
+++ b/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CA8391-B02D-45C5-9779-55E71F9692CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -283,31 +287,31 @@
     <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-GEOL%154%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%154</t>
   </si>
   <si>
-    <t>MATH 351%NUMERICAL METHODS%Azure Isaac%ED3-BME%90%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-TEL%140%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%140</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AE%100%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-COE%270%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%270</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-AUTO%40%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-CE%220%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%220</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-IND%72%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%72</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-EE%240%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%240</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-MARI%40%%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+    <t>MATH 351%NUMERICAL METHODS%Azure Isaac%ED3-BME%90%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-TEL%140%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%140</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AE%100%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-COE%270%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%270</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-AUTO%40%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-CE%220%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%220</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-IND%72%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%72</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-EE%240%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%240</t>
+  </si>
+  <si>
+    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-MARI%40%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
   </si>
   <si>
     <t>CE 271%ENGINEERING REPORTING%Tuffour Yaw Adubofour%ED2-CE%255%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
@@ -382,22 +386,22 @@
     <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MARI%46%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%46</t>
   </si>
   <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-IND%83%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%83</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-AERO%70%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%70</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MSE%100%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-METE%75%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%75</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-BME%136%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%136</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-AE%128%%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
+    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-IND%83%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%83</t>
+  </si>
+  <si>
+    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-AERO%70%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%70</t>
+  </si>
+  <si>
+    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MSE%100%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
+  </si>
+  <si>
+    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-METE%75%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%75</t>
+  </si>
+  <si>
+    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-BME%136%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%136</t>
+  </si>
+  <si>
+    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-AE%128%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
   </si>
   <si>
     <t>MATH 151%ALGEBRA%Ayekple Yao Elikem%ED1-EE%295%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2/EA/A110/VCR%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72/72/50/27/27/27/20</t>
@@ -532,10 +536,10 @@
     <t>AE 381%COMPUTER APPLICATION FOR AGRICULTURAL ENGINEERS%Amponsah William%ED3-AE%100%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
   </si>
   <si>
-    <t>AME 373%DESIGN OF AUTO MECHANICAL SYSTEMS%Andoh Prince Yaw%ED3-AUTO%40%%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
-  </si>
-  <si>
-    <t>MME 373%DESIGN OF MARINE MACHINE ELEMENTS%Andoh Prince Yaw%ED3-MARI%40%%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+    <t>AME 373%DESIGN OF AUTO MECHANICAL SYSTEMS%Andoh Prince Yaw%ED3-AUTO%40%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+  </si>
+  <si>
+    <t>MME 373%DESIGN OF MARINE MACHINE ELEMENTS%Andoh Prince Yaw%ED3-MARI%40%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
   </si>
   <si>
     <t>CENG 291%ENGINEERING IN SOCIETY%Kwegyir Daniel%ED2-EE%340%PB001/PB020/PB014/PB008/PB201/PB214/PB212/PB208/NEB-FF1%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/30/40/40/25/30/55</t>
@@ -559,7 +563,7 @@
     <t>MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-ME%225%COMPUTER BASED%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%225</t>
   </si>
   <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AERO%76%%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%76</t>
+    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AERO%76%COMPUTER BASED%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%76</t>
   </si>
   <si>
     <t>ME 255%STRENGTH OF MATERIALS I%Boahen Samuel%ED2-AE%165%PB001/PB020/PB014/PB008/PB201%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%35/35/35/25/35</t>
@@ -790,19 +794,19 @@
     <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-AUTO%82%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%82</t>
   </si>
   <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-BME%80%%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-MSE%80%%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-METE%59%%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%59</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PCE%65%%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PE%95%%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
+    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-BME%80%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
+  </si>
+  <si>
+    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-MSE%80%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
+  </si>
+  <si>
+    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-METE%59%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%59</t>
+  </si>
+  <si>
+    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PCE%65%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65</t>
+  </si>
+  <si>
+    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PE%95%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
   </si>
   <si>
     <t>ME 195%ENGINEERING TECHNOLOGY%Agyei Agyemang Anthony%ED1-ME%226%PB001/PB014/PB020/PB201/NEB-SF%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%38/38/38/38/74</t>
@@ -1015,19 +1019,19 @@
     <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-COE%270%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%270</t>
   </si>
   <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-IND%72%%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72</t>
-  </si>
-  <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Carole Fredua Amoako-Yirenkyi%ED3-AERO%76%%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%76</t>
-  </si>
-  <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-ME%230%%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%230</t>
-  </si>
-  <si>
-    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-PE%95%%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
-  </si>
-  <si>
-    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-ME%242%%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%242</t>
+    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-IND%72%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72</t>
+  </si>
+  <si>
+    <t>STAT 253%PROBABILITY AND STATISTICS%Carole Fredua Amoako-Yirenkyi%ED3-AERO%76%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%76</t>
+  </si>
+  <si>
+    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-ME%230%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%230</t>
+  </si>
+  <si>
+    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-PE%95%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
+  </si>
+  <si>
+    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-ME%242%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%242</t>
   </si>
   <si>
     <t>FC 181%FRENCH FOR COMMUNICATION PURPOSES I%Boakye-Agyeman Candy%ED2-COE%155%NEB-SF/NEB-FF2/NEB-TF%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65/25/65</t>
@@ -1108,9 +1112,6 @@
     <t>PE 473%SAFETY AND RELIABILITY ENGINEERING%Quaye Jonathan Atuquaye%ED4-PE%97%PB201/PB214/PB208%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/27</t>
   </si>
   <si>
-    <t>AERO 157%INTRODUCTION TO AVIATION TECHNOLOGY%Oppong David Kofi%ED1-AERO%90%NEB-TF%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%NEB-TF</t>
-  </si>
-  <si>
     <t>BME 471%BIOINSTRUMENTATION II%Acquah Isaac%ED4-BME%87%NAF1/EA/A110%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/23/24</t>
   </si>
   <si>
@@ -1144,9 +1145,6 @@
     <t>MME 353%MARINE ELECTRICAL TECHNOLOGY%Frimpong Emmanuel Asuming%ED3-MARI%40%VSLA%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
   </si>
   <si>
-    <t>MSE 455%FAILURE ANALYSIS AND NON-DESTRUCTIVE TESTING%Arthur Emmanuel Kwesi%ED4-MSE%64%NEB-SF%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%NEB-SF</t>
-  </si>
-  <si>
     <t>METE 453%METALLURGICAL FAILURE ANALYSIS AND NDTs%Arthur Emmanuel Kwesi%ED4-METE%53%A110/EA%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%28/25</t>
   </si>
   <si>
@@ -1192,12 +1190,6 @@
     <t>IE 451%FACILITIES DESIGN AND MATERIAL HANDLING%Sackey Samuel Mensah%ED4-IND%67%NEB-SF%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%67</t>
   </si>
   <si>
-    <t>CE 257%COMPUTER PROGRAMMING%Osei Jack Banahene%ED2-CE%255%PB01/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
-  </si>
-  <si>
-    <t>GE 381%ENGINEERING SURVEYING I%Obeng Kwame%ED3-CE%220%PB01/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/23/22</t>
-  </si>
-  <si>
     <t>ME 255%STRENGTH OF MATERIALS I%Dzebre Denis Edem Kwame%ED2-AUTO%85%VSLA/LT/303%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/20/25</t>
   </si>
   <si>
@@ -1225,9 +1217,6 @@
     <t>COE 475%COMPUTER NETWORKING%Akowuah Emmanuel Kofi%ED4-COE%160%COMPUTER BASED%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%160</t>
   </si>
   <si>
-    <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-COE%255%PB01/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/40/40/40/40/30/25</t>
-  </si>
-  <si>
     <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-BME%80%NAF1/EA/VCR%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/20/20</t>
   </si>
   <si>
@@ -1237,9 +1226,6 @@
     <t>PE 367%STATISTICS FOR PETROLEUM ENGINEERS%Adjei Stephen%ED3-PE%80%NEB-TF%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
   </si>
   <si>
-    <t>EE 367%POWER GENERATION  AND SUPPLY%Asigri Peter%ED3-EE%240%PB01/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%37/37/37/37/37/30/25</t>
-  </si>
-  <si>
     <t>CHE 461%COMPUTER OPTIMIZATION METHOD%Bonsu Jude Kwaku%ED4-CHE%8%A110 %Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%8</t>
   </si>
   <si>
@@ -1261,25 +1247,25 @@
     <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-AE%128%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%125</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-CE%245%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%245</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-MSE%100%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-PE%130%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-TEL%130%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-ME%226%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%226</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-MARI%46%%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%46</t>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%125</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-CE%245%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%245</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-MSE%100%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-PE%130%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-TEL%130%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-ME%226%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%226</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-MARI%46%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%46</t>
   </si>
   <si>
     <t>ME 363%AUTOMATIC CONTROL I%Faisal Wahib Adam%ED3-AERO%76%NEB-SF%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%76</t>
@@ -1306,9 +1292,6 @@
     <t>ME 259%APPLICATIONS OF COMPUTER GRAPHICS%Ayetor Godwin Kafui Kwesi%ED2-MARI%37%NAF1%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
   </si>
   <si>
-    <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-CHE%157%PB01/PB014/PB020/PB201/PB214%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%32/32/32/31/30</t>
-  </si>
-  <si>
     <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-PCE%65%A110/VCR/EA%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/20/20</t>
   </si>
   <si>
@@ -1321,22 +1304,22 @@
     <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-PCE%56%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%56</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-BME%136%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%136</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-METE%75%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%75</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-CHE%120%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%120</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOM%100%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-COE%262%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%262</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-IND%83%%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-BME%136%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%136</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-METE%75%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%75</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-CHE%120%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%120</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOM%100%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-COE%262%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%262</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-IND%83%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
   </si>
   <si>
     <t>PCE 457%CORROSION ENGINEERING%Anang Daniel Adjah%ED4-PCE%55%NEB-FF1%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%55</t>
@@ -1366,10 +1349,10 @@
     <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-EE%295%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%295</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-AUTO%85%%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%85</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Appiah Franklin Benjamin%ED1-AERO%70%%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%70</t>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-AUTO%85%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%85</t>
+  </si>
+  <si>
+    <t>ENGL 157%COMMUNICATION SKILLS I%Appiah Franklin Benjamin%ED1-AERO%70%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%70</t>
   </si>
   <si>
     <t>CE 359%SOIL MECHANICS%Charkley Frederick Nai%ED3-CE%220%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%35/35/35/35/35/20/25</t>
@@ -1480,9 +1463,6 @@
     <t>AE 459%ADVANCED FARM POWER AND MACHINERY%Aikins Stephen Hill Mends%ED4-AE%103%VSLA/303/304/LT%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/23/20/20</t>
   </si>
   <si>
-    <t>GED 357%BASIC HYDROLOGY%Appiah-Adjei Emmanuel Kwame%ED3-GEOL%158%PB001/PB014/PB020/PB201/P008%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%34/34/34/34/22</t>
-  </si>
-  <si>
     <t>GE 151%CARTOGRAPHY I%Quaye-Ballard Jonathan Arthur%ED1-GEOM%100%NAF1/EA/A110%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/30/30</t>
   </si>
   <si>
@@ -1495,9 +1475,6 @@
     <t>MME 355%BASIC SHIP STRUCTURE%Andoh Prince Yaw%ED3-MARI%40%VSLA%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
   </si>
   <si>
-    <t>EE 387%CLASSICAL CONTROL SYSTEMS%Opoku Daniel%ED3-EE%250%PB01/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%40/40/40/40/40/25/25</t>
-  </si>
-  <si>
     <t>CHE 467%BIOCHEMICAL TECHNOLOGY%Ankudey Emmanuel Godwin%ED4-CHE%33%PB001%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%33</t>
   </si>
   <si>
@@ -1516,9 +1493,6 @@
     <t>GE 463%LAND AND GEOGRAPHIC INFORMATION SYSTEM I%Forkuo Eric Kwabena%ED4-GEOM%93%NAF1/EA/A110%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%43/25/25</t>
   </si>
   <si>
-    <t>EE 463%SPECIAL ELECTRICAL MACHINES%Kwegyir Daniel%ED4-EE%157%PB08/PB014/PB020/PB201/PB214%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/35/35/32/30</t>
-  </si>
-  <si>
     <t>CE 479%ENGINEERING AND ENVIRONMENTAL GEOPHYSICS%Owusu-Nimo Frederick%ED4-CE%95%NEB-SF/NEB-FF2%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65/30</t>
   </si>
   <si>
@@ -1546,9 +1520,6 @@
     <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-AERO%70%NEB-SF%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%70</t>
   </si>
   <si>
-    <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-ME%226%PB01/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/26/25</t>
-  </si>
-  <si>
     <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sekyere Charles Kofi Kafui%ED1-MARI%46%NEB-FF1%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%46</t>
   </si>
   <si>
@@ -1601,19 +1572,52 @@
   </si>
   <si>
     <t>CE 355%HYDROLOGY%Adjei Kwaku Amaning%ED3-CE%220%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Friday, 24 April 2026%Session, 3 (3:00 PM - 5:00 PM)%70/70/55/25</t>
+  </si>
+  <si>
+    <t>CE 257%COMPUTER PROGRAMMING%Osei Jack Banahene%ED2-CE%255%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
+  </si>
+  <si>
+    <t>GE 381%ENGINEERING SURVEYING I%Obeng Kwame%ED3-CE%220%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/23/22</t>
+  </si>
+  <si>
+    <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/40/40/40/40/30/25</t>
+  </si>
+  <si>
+    <t>EE 367%POWER GENERATION  AND SUPPLY%Asigri Peter%ED3-EE%240%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%37/37/37/37/37/30/25</t>
+  </si>
+  <si>
+    <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-CHE%157%PB001/PB014/PB020/PB201/PB214%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%32/32/32/31/30</t>
+  </si>
+  <si>
+    <t>GED 357%BASIC HYDROLOGY%Appiah-Adjei Emmanuel Kwame%ED3-GEOL%158%PB001/PB014/PB020/PB201/PB008%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%34/34/34/34/22</t>
+  </si>
+  <si>
+    <t>EE 387%CLASSICAL CONTROL SYSTEMS%Opoku Daniel%ED3-EE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%40/40/40/40/40/25/25</t>
+  </si>
+  <si>
+    <t>EE 463%SPECIAL ELECTRICAL MACHINES%Kwegyir Daniel%ED4-EE%157%PB008/PB014/PB020/PB201/PB214%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/35/35/32/30</t>
+  </si>
+  <si>
+    <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-ME%226%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/26/25</t>
+  </si>
+  <si>
+    <t>AERO 157%INTRODUCTION TO AVIATION TECHNOLOGY%Oppong David Kofi%ED1-AERO%90%NEB-TF%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
+  </si>
+  <si>
+    <t>MSE 455%FAILURE ANALYSIS AND NON-DESTRUCTIVE TESTING%Arthur Emmanuel Kwesi%ED4-MSE%64%NEB-SF%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%64</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1976,2662 +1980,2665 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A530"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="204.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
+    <row r="416" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
+    <row r="417" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
+    <row r="418" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
+    <row r="419" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
+    <row r="420" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
+    <row r="421" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
+    <row r="422" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
+    <row r="423" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
+    <row r="425" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
+    <row r="426" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
+    <row r="427" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
+    <row r="428" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
+    <row r="429" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
+    <row r="430" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
+    <row r="431" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
+    <row r="432" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
+    <row r="434" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
+    <row r="435" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
+    <row r="436" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
+    <row r="437" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
+    <row r="438" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
+    <row r="439" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
+    <row r="440" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
+    <row r="441" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
+    <row r="442" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
+    <row r="443" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
+    <row r="444" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
+    <row r="445" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
+    <row r="446" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
+    <row r="447" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
+    <row r="448" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
+    <row r="449" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
+    <row r="450" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
+    <row r="451" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
+    <row r="452" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
+    <row r="453" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
+    <row r="454" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
+    <row r="455" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
+    <row r="456" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
+    <row r="457" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
+    <row r="458" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
+    <row r="459" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
+    <row r="460" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
+    <row r="461" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
+    <row r="462" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
+    <row r="463" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
+    <row r="464" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
+    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
+    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
+    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
+    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
+    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
+    <row r="470" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
+    <row r="471" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
+    <row r="472" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
+    <row r="473" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
+    <row r="474" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
+    <row r="475" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
+    <row r="476" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
+    <row r="477" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
+    <row r="478" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
+    <row r="479" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
+    <row r="480" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
+    <row r="481" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
+    <row r="482" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
+    <row r="483" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
+    <row r="484" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
+    <row r="485" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
+    <row r="486" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
+    <row r="487" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
+    <row r="488" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A482" t="s">
+    <row r="489" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
+    <row r="490" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
+    <row r="492" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
+    <row r="493" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
+    <row r="494" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
+    <row r="495" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
+    <row r="497" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
+    <row r="498" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
+    <row r="499" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
+    <row r="500" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
+    <row r="501" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
+    <row r="502" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
+    <row r="504" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
+    <row r="505" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
+    <row r="506" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+    <row r="507" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+    <row r="508" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+    <row r="509" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
+    <row r="510" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
+    <row r="511" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
+    <row r="512" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
+    <row r="514" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
+    <row r="515" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
+    <row r="516" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
+    <row r="517" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A507" t="s">
+    <row r="518" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A508" t="s">
+    <row r="519" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A509" t="s">
+    <row r="520" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A510" t="s">
+    <row r="521" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
+    <row r="522" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
+    <row r="523" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
+    <row r="524" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A514" t="s">
+    <row r="525" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A515" t="s">
+    <row r="526" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
+    <row r="527" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A517" t="s">
+    <row r="528" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
+    <row r="529" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A519" t="s">
+    <row r="530" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
         <v>518</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A520" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A521" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A522" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A529" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A530" t="s">
-        <v>529</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
+++ b/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CA8391-B02D-45C5-9779-55E71F9692CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C49D99-C219-4AEF-AE48-88C8BA0E97D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <t>EE 261%DC MACHINES%Effah Francis Boafo%ED2-EE%345%NEB-TF/NEB-SF/NEB-FF1/PB001/PB020/PB014/PB201%Tuesday, 7 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72/72/49/38/38/38/38</t>
   </si>
   <si>
-    <t>COE 363%DATA STRUCTURES AND ALGORITHMS%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED3-COE%270%COMPUTER BASED%Tuesday, 7 April 2026%Session, 2 (12:00 PM - 2:00 PM)%270</t>
+    <t xml:space="preserve">COE 363%DATA STRUCTURES AND ALGORITHMS%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED3-COE%270%Computer Based %Tuesday, 7 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>CE 255%THEORY OF STRUCTURES%Ampofo James Wiafe%ED2-CE%255%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Tuesday, 7 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/28/27</t>
@@ -146,7 +146,7 @@
     <t>BME 461%BIOMECHANICS I%Odame Prince%ED4-BME%87%N1/N2/RMB/303%Wednesday, 8 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/20/20/22</t>
   </si>
   <si>
-    <t>COE 363%DATA STRUCTURES AND ALGORITHMS%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED3-COE%270%COMPUTER BASED%Wednesday, 8 April 2026%Session, 2 (12:00 PM - 2:00 PM)%270</t>
+    <t xml:space="preserve">COE 363%DATA STRUCTURES AND ALGORITHMS%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED3-COE%270%Computer Based %Wednesday, 8 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>COE 453%DISTRIBUTED COMPUTING%Keelson Eliel%ED4-COE%140%NEB-TF/NEB-SF%Wednesday, 8 April 2026%Session, 2 (12:00 PM - 2:00 PM)%80/60</t>
@@ -284,34 +284,34 @@
     <t>ME 251%INTRODUCTION TO FLUID MECHANICS%Tay Godwin Fabiola Kwaku%ED2-MARI%37%PB214%Thursday, 9 April 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
   </si>
   <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-GEOL%154%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%154</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL METHODS%Azure Isaac%ED3-BME%90%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-TEL%140%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%140</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AE%100%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-COE%270%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%270</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-AUTO%40%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-CE%220%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%220</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-IND%72%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%72</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-EE%240%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%240</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-MARI%40%COMPUTER BASED%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-GEOL%154%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL METHODS%Azure Isaac%ED3-BME%90%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-TEL%140%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AE%100%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-COE%270%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-AUTO%40%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-CE%220%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-IND%72%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-EE%240%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Awashie Gaston Edem%ED3-MARI%40%Computer Based %Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>CE 271%ENGINEERING REPORTING%Tuffour Yaw Adubofour%ED2-CE%255%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Thursday, 9 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
@@ -383,25 +383,25 @@
     <t>METE 457%CORROSION OF ENGINEERING MATERIALS%Andrews Anthony%ED4-METE%53%NEB-FF1%Thursday, 9 April 2026%Session, 3 (3:00 PM - 5:00 PM)%53</t>
   </si>
   <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MARI%46%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%46</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-IND%83%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%83</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-AERO%70%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%70</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MSE%100%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-METE%75%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%75</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-BME%136%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%136</t>
-  </si>
-  <si>
-    <t>MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-AE%128%COMPUTER BASED%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MARI%46%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-IND%83%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-AERO%70%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-MSE%100%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Fosu Gabriel Obed%ED1-METE%75%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-BME%136%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 151%ALGEBRA%Asamoah Joshua Kiddy Kwasi%ED1-AE%128%Computer Based %Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
   </si>
   <si>
     <t>MATH 151%ALGEBRA%Ayekple Yao Elikem%ED1-EE%295%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2/EA/A110/VCR%Friday, 10 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72/72/50/27/27/27/20</t>
@@ -533,13 +533,13 @@
     <t>CHE 261%COMPUTER APPLICATIONS FOR ENGINEERS%Anang Daniel Adjah%ED2-CHE%157%NEB-FF2/NEB-SF/NEB-TF%Monday, 13 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/66/66</t>
   </si>
   <si>
-    <t>AE 381%COMPUTER APPLICATION FOR AGRICULTURAL ENGINEERS%Amponsah William%ED3-AE%100%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>AME 373%DESIGN OF AUTO MECHANICAL SYSTEMS%Andoh Prince Yaw%ED3-AUTO%40%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
-  </si>
-  <si>
-    <t>MME 373%DESIGN OF MARINE MACHINE ELEMENTS%Andoh Prince Yaw%ED3-MARI%40%COMPUTER BASED%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40</t>
+    <t xml:space="preserve">AE 381%COMPUTER APPLICATION FOR AGRICULTURAL ENGINEERS%Amponsah William%ED3-AE%100%Computer Based %Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AME 373%DESIGN OF AUTO MECHANICAL SYSTEMS%Andoh Prince Yaw%ED3-AUTO%40%Computer Based %Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MME 373%DESIGN OF MARINE MACHINE ELEMENTS%Andoh Prince Yaw%ED3-MARI%40%Computer Based %Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>CENG 291%ENGINEERING IN SOCIETY%Kwegyir Daniel%ED2-EE%340%PB001/PB020/PB014/PB008/PB201/PB214/PB212/PB208/NEB-FF1%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/30/40/40/25/30/55</t>
@@ -560,10 +560,10 @@
     <t>ME 161%BASIC MECHANICS%Dzebre Denis Edem Kwame%ED1-GEOM%100%NAF1/EA/A110%Monday, 13 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/30/30</t>
   </si>
   <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-ME%225%COMPUTER BASED%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%225</t>
-  </si>
-  <si>
-    <t>MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AERO%76%COMPUTER BASED%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%76</t>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Azure Isaac%ED3-ME%225%Computer Based %Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 351%NUMERICAL ANALYSIS%Borkor Reindorf Nartey%ED3-AERO%76%Computer Based %Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>ME 255%STRENGTH OF MATERIALS I%Boahen Samuel%ED2-AE%165%PB001/PB020/PB014/PB008/PB201%Monday, 13 April 2026%Session, 3 (3:00 PM - 5:00 PM)%35/35/35/25/35</t>
@@ -758,7 +758,7 @@
     <t>TE 351%INFORMATION THEORY AND CODING%Obour Agyekum Kwame Opuni-Boachie%ED3-TEL%140%NEB-TF/NEB-SF%Wednesday, 15 April 2026%Session, 2 (12:00 PM - 2:00 PM)%70/70</t>
   </si>
   <si>
-    <t>GE 371%SURVEY ADJUSTMENT I%Fosu Collins%ED3-GEOM%125%COMPUTER BASED%Wednesday, 15 April 2026%Session, 3 (3:00 PM - 5:00 PM)%125</t>
+    <t xml:space="preserve">GE 371%SURVEY ADJUSTMENT I%Fosu Collins%ED3-GEOM%125%Computer Based %Wednesday, 15 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>CHE 261%COMPUTER APPLICATIONS FOR ENGINEERS%Bonsu Jude Kwaku%ED2-PCE%65%NEB-TF%Wednesday, 15 April 2026%Session, 3 (3:00 PM - 5:00 PM)%65</t>
@@ -791,22 +791,22 @@
     <t>GE 475%RESEARCH METHODS%Duker Alfred Alan%ED4-GEOM%93%EA/A110/NAF1 %Wednesday, 15 April 2026%Session, 3 (3:00 PM - 5:00 PM)%27/26/40</t>
   </si>
   <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-AUTO%82%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%82</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-BME%80%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-MSE%80%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-METE%59%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%59</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PCE%65%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65</t>
-  </si>
-  <si>
-    <t>MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PE%95%COMPUTER BASED%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-AUTO%82%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-BME%80%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-MSE%80%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Asamoah Joshua Kiddy Kwasi%ED2-METE%59%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PCE%65%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 251%DIFFERENTIAL EQUATIONS%Eghan Rhydal Esi%ED2-PE%95%Computer Based %Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
   </si>
   <si>
     <t>ME 195%ENGINEERING TECHNOLOGY%Agyei Agyemang Anthony%ED1-ME%226%PB001/PB014/PB020/PB201/NEB-SF%Thursday, 16 April 2026%Session, 1 (8:30 AM - 10:30 AM)%38/38/38/38/74</t>
@@ -974,7 +974,7 @@
     <t>EE 265%ELECTRICAL SERVICES DESIGN%Kwegyir Daniel%ED2-EE%340%PB001/PB020/PB014/PB008/PB201/PB214/PB212/PB208/NEB-FF1%Friday, 17 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/30/40/40/25/30/55</t>
   </si>
   <si>
-    <t>COE 281%PROGRAMMING AND PROBLEM SOLVING%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED2-COE%255%COMPUTER BASED%Friday, 17 April 2026%Session, 3 (3:00 PM - 5:00 PM)%255</t>
+    <t xml:space="preserve">COE 281%PROGRAMMING AND PROBLEM SOLVING%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED2-COE%255%Computer Based %Friday, 17 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>ME 261%ENGINEERING MECHANICS II: DYNAMICS%Ampofo Joshua%ED2-ME%245%PB001/PB020/PB014/PB008/PB201/PB214/PB212%Friday, 17 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/40/40/30/40/35/20</t>
@@ -1016,22 +1016,22 @@
     <t>AE 353%AGRICULTURAL MATERIALS HANDLING AND PROCESSING%Akowuah Joseph Oppong%ED3-AE%100%NAF1/EA/A110/VCR%Friday, 17 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/20/20/20</t>
   </si>
   <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-COE%270%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%270</t>
-  </si>
-  <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-IND%72%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72</t>
-  </si>
-  <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Carole Fredua Amoako-Yirenkyi%ED3-AERO%76%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%76</t>
-  </si>
-  <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-ME%230%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%230</t>
-  </si>
-  <si>
-    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-PE%95%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
-  </si>
-  <si>
-    <t>ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-ME%242%COMPUTER BASED%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%242</t>
+    <t xml:space="preserve">STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-COE%270%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-IND%72%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT 253%PROBABILITY AND STATISTICS%Carole Fredua Amoako-Yirenkyi%ED3-AERO%76%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-ME%230%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-PE%95%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME 255%STRENGTH OF MATERIALS I%Andoh Prince Yaw%ED2-ME%242%Computer Based %Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
   </si>
   <si>
     <t>FC 181%FRENCH FOR COMMUNICATION PURPOSES I%Boakye-Agyeman Candy%ED2-COE%155%NEB-SF/NEB-FF2/NEB-TF%Monday, 20 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65/25/65</t>
@@ -1112,10 +1112,13 @@
     <t>PE 473%SAFETY AND RELIABILITY ENGINEERING%Quaye Jonathan Atuquaye%ED4-PE%97%PB201/PB214/PB208%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/27</t>
   </si>
   <si>
+    <t>AERO 157%INTRODUCTION TO AVIATION TECHNOLOGY%Oppong David Kofi%ED1-AERO%90%NEB-TF%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
+  </si>
+  <si>
     <t>BME 471%BIOINSTRUMENTATION II%Acquah Isaac%ED4-BME%87%NAF1/EA/A110%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/23/24</t>
   </si>
   <si>
-    <t>ME 455%FINITE ELEMENT METHODS%Andoh Prince Yaw%ED4-ME%140%COMPUTER BASED%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%140</t>
+    <t xml:space="preserve">ME 455%FINITE ELEMENT METHODS%Andoh Prince Yaw%ED4-ME%140%Computer Based %Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>MSE 359%MATERIALS PROCESSING LABORATORY%Dzikunu Perseverance%ED3-MSE%89%PB201/PB214/PB008%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%34/34/21</t>
@@ -1154,7 +1157,7 @@
     <t>AME 371%LAND VEHICLE DESIGN%Ayetor Godwin Kafui Kwesi%ED3-AUTO%40%PB214%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
   </si>
   <si>
-    <t>STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-GEOM%93%COMPUTER BASED%Tuesday, 21 April 2026%Session, 1 (8:30 AM - 10:30 AM)%93</t>
+    <t xml:space="preserve">STAT 253%PROBABILITY AND STATISTICS%Amoako-Yirenkyi Carole Fredua%ED3-GEOM%93%Computer Based %Tuesday, 21 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
   </si>
   <si>
     <t>IE 367%ETHICS, CONTRACT &amp; PRODUCT LIABILITY LAW%Asiedu Charlotte%ED3-IND%72%NEB-TF%Tuesday, 21 April 2026%Session, 1 (8:30 AM - 10:30 AM)%72</t>
@@ -1190,6 +1193,12 @@
     <t>IE 451%FACILITIES DESIGN AND MATERIAL HANDLING%Sackey Samuel Mensah%ED4-IND%67%NEB-SF%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%67</t>
   </si>
   <si>
+    <t>CE 257%COMPUTER PROGRAMMING%Osei Jack Banahene%ED2-CE%255%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
+  </si>
+  <si>
+    <t>GE 381%ENGINEERING SURVEYING I%Obeng Kwame%ED3-CE%220%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/23/22</t>
+  </si>
+  <si>
     <t>ME 255%STRENGTH OF MATERIALS I%Dzebre Denis Edem Kwame%ED2-AUTO%85%VSLA/LT/303%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/20/25</t>
   </si>
   <si>
@@ -1214,7 +1223,10 @@
     <t>CHE 253%CHEMICAL ENGINEERING THERMODYNAMICS I%Dogbe Eunice Sefakor Aku%ED2-PCE%65%NEB-FF1/NEB-FF2%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/25</t>
   </si>
   <si>
-    <t>COE 475%COMPUTER NETWORKING%Akowuah Emmanuel Kofi%ED4-COE%160%COMPUTER BASED%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%160</t>
+    <t xml:space="preserve">COE 475%COMPUTER NETWORKING%Akowuah Emmanuel Kofi%ED4-COE%160%Computer Based %Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/40/40/40/40/30/25</t>
   </si>
   <si>
     <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-BME%80%NAF1/EA/VCR%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/20/20</t>
@@ -1226,6 +1238,9 @@
     <t>PE 367%STATISTICS FOR PETROLEUM ENGINEERS%Adjei Stephen%ED3-PE%80%NEB-TF%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
   </si>
   <si>
+    <t>EE 367%POWER GENERATION  AND SUPPLY%Asigri Peter%ED3-EE%240%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%37/37/37/37/37/30/25</t>
+  </si>
+  <si>
     <t>CHE 461%COMPUTER OPTIMIZATION METHOD%Bonsu Jude Kwaku%ED4-CHE%8%A110 %Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%8</t>
   </si>
   <si>
@@ -1244,28 +1259,28 @@
     <t>TE 455%MICROWAVE ENGINEERING%Abdul-Rahman Ahmed%ED4-TEL%140%VSLA/LT/N1/303/N2%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/25/25/30/20</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-AE%128%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%125</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-CE%245%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%245</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-MSE%100%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-PE%130%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-TEL%130%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-ME%226%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%226</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-MARI%46%COMPUTER BASED%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%46</t>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-AE%128%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-CE%245%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-MSE%100%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-PE%130%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-TEL%130%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-ME%226%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-MARI%46%Computer Based %Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%Computer Based </t>
   </si>
   <si>
     <t>ME 363%AUTOMATIC CONTROL I%Faisal Wahib Adam%ED3-AERO%76%NEB-SF%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%76</t>
@@ -1292,6 +1307,9 @@
     <t>ME 259%APPLICATIONS OF COMPUTER GRAPHICS%Ayetor Godwin Kafui Kwesi%ED2-MARI%37%NAF1%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
   </si>
   <si>
+    <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-CHE%157%PB001/PB014/PB020/PB201/PB214%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%32/32/32/31/30</t>
+  </si>
+  <si>
     <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-PCE%65%A110/VCR/EA%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/20/20</t>
   </si>
   <si>
@@ -1301,25 +1319,25 @@
     <t>ME 355%STRENGTH OF MATERIALS II%Agyei Agyemang Anthony%ED3-AE%100%VSLA/LT/RMB/RMA%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%40/20/20/20</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-PCE%56%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%56</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-BME%136%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%136</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-METE%75%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%75</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-CHE%120%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%120</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOM%100%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-COE%262%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%262</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-IND%83%COMPUTER BASED%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-PCE%56%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-BME%136%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-METE%75%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-CHE%120%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-GEOM%100%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Alhassan Yakubu%ED1-COE%262%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Yeboah Philomena Ama Okyeso%ED1-IND%83%Computer Based %Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>PCE 457%CORROSION ENGINEERING%Anang Daniel Adjah%ED4-PCE%55%NEB-FF1%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%55</t>
@@ -1346,13 +1364,13 @@
     <t>TE 465%DIGITAL INTEGRATED CIRCUITS%Affum Emmanuel Ampoma%ED4-TEL%55%NEB-SF%Wednesday, 22 April 2026%Session, 2 (12:00 PM - 2:00 PM)%55</t>
   </si>
   <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-EE%295%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%295</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-AUTO%85%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%85</t>
-  </si>
-  <si>
-    <t>ENGL 157%COMMUNICATION SKILLS I%Appiah Franklin Benjamin%ED1-AERO%70%COMPUTER BASED%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%70</t>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-EE%295%Computer Based %Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Sarfo-Adu Kwasi%ED1-AUTO%85%Computer Based %Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGL 157%COMMUNICATION SKILLS I%Appiah Franklin Benjamin%ED1-AERO%70%Computer Based %Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%Computer Based </t>
   </si>
   <si>
     <t>CE 359%SOIL MECHANICS%Charkley Frederick Nai%ED3-CE%220%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Wednesday, 22 April 2026%Session, 3 (3:00 PM - 5:00 PM)%35/35/35/35/35/20/25</t>
@@ -1463,6 +1481,9 @@
     <t>AE 459%ADVANCED FARM POWER AND MACHINERY%Aikins Stephen Hill Mends%ED4-AE%103%VSLA/303/304/LT%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/23/20/20</t>
   </si>
   <si>
+    <t>GED 357%BASIC HYDROLOGY%Appiah-Adjei Emmanuel Kwame%ED3-GEOL%158%PB001/PB014/PB020/PB201/PB008%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%34/34/34/34/22</t>
+  </si>
+  <si>
     <t>GE 151%CARTOGRAPHY I%Quaye-Ballard Jonathan Arthur%ED1-GEOM%100%NAF1/EA/A110%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/30/30</t>
   </si>
   <si>
@@ -1475,6 +1496,9 @@
     <t>MME 355%BASIC SHIP STRUCTURE%Andoh Prince Yaw%ED3-MARI%40%VSLA%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
   </si>
   <si>
+    <t>EE 387%CLASSICAL CONTROL SYSTEMS%Opoku Daniel%ED3-EE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%40/40/40/40/40/25/25</t>
+  </si>
+  <si>
     <t>CHE 467%BIOCHEMICAL TECHNOLOGY%Ankudey Emmanuel Godwin%ED4-CHE%33%PB001%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%33</t>
   </si>
   <si>
@@ -1493,6 +1517,9 @@
     <t>GE 463%LAND AND GEOGRAPHIC INFORMATION SYSTEM I%Forkuo Eric Kwabena%ED4-GEOM%93%NAF1/EA/A110%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%43/25/25</t>
   </si>
   <si>
+    <t>EE 463%SPECIAL ELECTRICAL MACHINES%Kwegyir Daniel%ED4-EE%157%PB008/PB014/PB020/PB201/PB214%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/35/35/32/30</t>
+  </si>
+  <si>
     <t>CE 479%ENGINEERING AND ENVIRONMENTAL GEOPHYSICS%Owusu-Nimo Frederick%ED4-CE%95%NEB-SF/NEB-FF2%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%65/30</t>
   </si>
   <si>
@@ -1520,6 +1547,9 @@
     <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-AERO%70%NEB-SF%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%70</t>
   </si>
   <si>
+    <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-ME%226%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/26/25</t>
+  </si>
+  <si>
     <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sekyere Charles Kofi Kafui%ED1-MARI%46%NEB-FF1%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%46</t>
   </si>
   <si>
@@ -1572,36 +1602,6 @@
   </si>
   <si>
     <t>CE 355%HYDROLOGY%Adjei Kwaku Amaning%ED3-CE%220%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Friday, 24 April 2026%Session, 3 (3:00 PM - 5:00 PM)%70/70/55/25</t>
-  </si>
-  <si>
-    <t>CE 257%COMPUTER PROGRAMMING%Osei Jack Banahene%ED2-CE%255%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%40/40/40/40/40/30/25</t>
-  </si>
-  <si>
-    <t>GE 381%ENGINEERING SURVEYING I%Obeng Kwame%ED3-CE%220%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/23/22</t>
-  </si>
-  <si>
-    <t>COE 271%SEMICONDUCTOR DEVICES%Kommey Benjamin%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%40/40/40/40/40/30/25</t>
-  </si>
-  <si>
-    <t>EE 367%POWER GENERATION  AND SUPPLY%Asigri Peter%ED3-EE%240%PB001/PB014/PB020/PB201/PB214/PB208/PB008%Tuesday, 21 April 2026%Session, 3 (3:00 PM - 5:00 PM)%37/37/37/37/37/30/25</t>
-  </si>
-  <si>
-    <t>CHE 257%ANALYTICAL CHEMISTRY FOR CHEMICAL ENGINEERS%Boakye Patrick%ED2-CHE%157%PB001/PB014/PB020/PB201/PB214%Wednesday, 22 April 2026%Session, 1 (8:30 AM - 10:30 AM)%32/32/32/31/30</t>
-  </si>
-  <si>
-    <t>GED 357%BASIC HYDROLOGY%Appiah-Adjei Emmanuel Kwame%ED3-GEOL%158%PB001/PB014/PB020/PB201/PB008%Thursday, 23 April 2026%Session, 3 (3:00 PM - 5:00 PM)%34/34/34/34/22</t>
-  </si>
-  <si>
-    <t>EE 387%CLASSICAL CONTROL SYSTEMS%Opoku Daniel%ED3-EE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%40/40/40/40/40/25/25</t>
-  </si>
-  <si>
-    <t>EE 463%SPECIAL ELECTRICAL MACHINES%Kwegyir Daniel%ED4-EE%157%PB008/PB014/PB020/PB201/PB214%Friday, 24 April 2026%Session, 1 (8:30 AM - 10:30 AM)%25/35/35/32/30</t>
-  </si>
-  <si>
-    <t>ME 157%INTRODUCTION TO INFORMATION TECHNOLOGY%Sackey Michael Nii%ED1-ME%226%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 24 April 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/26/25</t>
-  </si>
-  <si>
-    <t>AERO 157%INTRODUCTION TO AVIATION TECHNOLOGY%Oppong David Kofi%ED1-AERO%90%NEB-TF%Monday, 20 April 2026%Session, 2 (12:00 PM - 2:00 PM)%90</t>
   </si>
   <si>
     <t>MSE 455%FAILURE ANALYSIS AND NON-DESTRUCTIVE TESTING%Arthur Emmanuel Kwesi%ED4-MSE%64%NEB-SF%Monday, 20 April 2026%Session, 3 (3:00 PM - 5:00 PM)%64</t>
@@ -1984,7 +1984,7 @@
   <dimension ref="A1:A530"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="204.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="203.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -3814,62 +3814,62 @@
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>528</v>
+        <v>365</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.35">
@@ -3879,762 +3879,762 @@
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>519</v>
+        <v>392</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>520</v>
+        <v>393</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>521</v>
+        <v>403</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>522</v>
+        <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>523</v>
+        <v>430</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
+++ b/src/outputs/Examtt2k25_26_FS-cleaned.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C49D99-C219-4AEF-AE48-88C8BA0E97D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCEC5DF-D300-477B-BC75-3515B6B3478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
